--- a/WpfUI/Resources/Templates/DotnetNetworking/Question/Detail.xlsx
+++ b/WpfUI/Resources/Templates/DotnetNetworking/Question/Detail.xlsx
@@ -5,43 +5,57 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnFall25\Code\Recorder_NetWorking\WpfUI\Resources\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Q1\Q1\TC2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6479BA44-63C8-4783-B450-E51384F94B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E476D155-B93E-4D48-B1C4-6AADCB3BC765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3F0699F3-5564-4039-86D9-9754FBE2E8E5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="User" sheetId="1" r:id="rId1"/>
+    <sheet name="Client" sheetId="2" r:id="rId2"/>
+    <sheet name="Server" sheetId="3" r:id="rId3"/>
+    <sheet name="Database" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Console</t>
+  </si>
+  <si>
+    <t>Query</t>
+  </si>
+  <si>
+    <t>ExpectedData</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,8 +78,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -379,10 +402,122 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34077DD0-79C5-4554-89D9-89C1777D4E5D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="3" width="10" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="2" width="10" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="2" width="10" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="29">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>